--- a/labe3.xlsx
+++ b/labe3.xlsx
@@ -1,16 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\Desktop\IskIn\YPM-IskIm\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -22,60 +26,56 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="15">
   <si>
-    <t xml:space="preserve">класс</t>
+    <t>класс</t>
   </si>
   <si>
-    <t xml:space="preserve">x0</t>
+    <t>x0</t>
   </si>
   <si>
-    <t xml:space="preserve">x1</t>
+    <t>x1</t>
   </si>
   <si>
-    <t xml:space="preserve">x2</t>
+    <t>x2</t>
   </si>
   <si>
-    <t xml:space="preserve">w0</t>
+    <t>w0</t>
   </si>
   <si>
-    <t xml:space="preserve">w1</t>
+    <t>w1</t>
   </si>
   <si>
-    <t xml:space="preserve">w2</t>
+    <t>w2</t>
   </si>
   <si>
-    <t xml:space="preserve">z</t>
+    <t>z</t>
   </si>
   <si>
-    <t xml:space="preserve">y</t>
+    <t>y</t>
   </si>
   <si>
-    <t xml:space="preserve">верно?</t>
+    <t>верно?</t>
   </si>
   <si>
-    <t xml:space="preserve">-</t>
+    <t>-</t>
   </si>
   <si>
-    <t xml:space="preserve">+</t>
+    <t>+</t>
   </si>
   <si>
-    <t xml:space="preserve">X</t>
+    <t>X</t>
   </si>
   <si>
-    <t xml:space="preserve">X2</t>
+    <t>X2</t>
   </si>
   <si>
-    <t xml:space="preserve">X2=-(w0+w1x)/w2</t>
+    <t>X2=-(w0+w1x)/w2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,39 +84,12 @@
       <charset val="204"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF595959"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF595959"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -128,190 +101,147 @@
     </fill>
   </fills>
   <borders count="11">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right/>
-      <top style="medium"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
-      <top style="medium"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
-      <top style="medium"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
-      <right style="medium"/>
-      <top style="medium"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
-      <right style="medium"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
-      <bottom style="medium"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
-      <right style="medium"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="medium"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -325,6 +255,7 @@
       </fill>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -383,15 +314,33 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF385623"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
@@ -400,10 +349,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.00545960417869706"/>
+          <c:x val="5.4596041786970596E-3"/>
           <c:y val="0"/>
-          <c:w val="0.976534201270408"/>
-          <c:h val="0.9827566518214"/>
+          <c:w val="0.97653420127040802"/>
+          <c:h val="0.98275665182140004"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -413,9 +362,6 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="ed7d31"/>
-            </a:solidFill>
             <a:ln w="19080">
               <a:noFill/>
             </a:ln>
@@ -425,97 +371,116 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="ed7d31"/>
+                <a:srgbClr val="ED7D31"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
           <c:dPt>
             <c:idx val="0"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="2a6099"/>
+                  <a:srgbClr val="2A6099"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-B542-40D1-9C6F-5E77D2813FE7}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="2a6099"/>
+                  <a:srgbClr val="2A6099"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-B542-40D1-9C6F-5E77D2813FE7}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="2a6099"/>
+                  <a:srgbClr val="2A6099"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-B542-40D1-9C6F-5E77D2813FE7}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="2a6099"/>
+                  <a:srgbClr val="2A6099"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-B542-40D1-9C6F-5E77D2813FE7}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="2a6099"/>
+                  <a:srgbClr val="2A6099"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-B542-40D1-9C6F-5E77D2813FE7}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
-            <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:srgbClr val="ed7d31"/>
-                </a:solidFill>
-              </c:spPr>
-            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-B542-40D1-9C6F-5E77D2813FE7}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="square"/>
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
                       <a:latin typeface="Calibri"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ru-RU"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="r"/>
@@ -524,22 +489,29 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator>; </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-B542-40D1-9C6F-5E77D2813FE7}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="square"/>
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
                       <a:latin typeface="Calibri"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ru-RU"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="r"/>
@@ -548,22 +520,29 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator>; </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-B542-40D1-9C6F-5E77D2813FE7}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="square"/>
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
                       <a:latin typeface="Calibri"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ru-RU"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="r"/>
@@ -572,22 +551,29 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator>; </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-B542-40D1-9C6F-5E77D2813FE7}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="square"/>
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
                       <a:latin typeface="Calibri"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ru-RU"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="r"/>
@@ -596,22 +582,29 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator>; </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-B542-40D1-9C6F-5E77D2813FE7}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="4"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="square"/>
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
                       <a:latin typeface="Calibri"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ru-RU"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="r"/>
@@ -620,22 +613,29 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator>; </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-B542-40D1-9C6F-5E77D2813FE7}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="8"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="square"/>
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
                       <a:latin typeface="Calibri"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ru-RU"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="r"/>
@@ -644,20 +644,33 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator>; </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-B542-40D1-9C6F-5E77D2813FE7}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="r"/>
@@ -666,8 +679,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -693,7 +707,7 @@
                   <c:v>-0.3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-1.1</c:v>
+                  <c:v>-1.1000000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0.7</c:v>
@@ -753,25 +767,19 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-B542-40D1-9C6F-5E77D2813FE7}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:strRef>
-              <c:f>"Прямая"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Прямая</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Прямая</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="385623"/>
-            </a:solidFill>
             <a:ln w="25560">
               <a:noFill/>
             </a:ln>
@@ -786,18 +794,26 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="r"/>
@@ -806,8 +822,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -857,37 +874,50 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>-2.85714285714286</c:v>
+                  <c:v>-2.8571428571428572</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-2.14285714285714</c:v>
+                  <c:v>-2.1428571428571428</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-1.42857142857143</c:v>
+                  <c:v>-1.4285714285714286</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0.714285714285714</c:v>
+                  <c:v>-0.7142857142857143</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.714285714285714</c:v>
+                  <c:v>0.7142857142857143</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.42857142857143</c:v>
+                  <c:v>1.4285714285714286</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.14285714285714</c:v>
+                  <c:v>2.1428571428571428</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.85714285714286</c:v>
+                  <c:v>2.8571428571428572</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-B542-40D1-9C6F-5E77D2813FE7}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="87998239"/>
         <c:axId val="1100220"/>
       </c:scatterChart>
@@ -904,7 +934,7 @@
           <c:spPr>
             <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="d9d9d9"/>
+                <a:srgbClr val="D9D9D9"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -917,7 +947,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="bfbfbf"/>
+              <a:srgbClr val="BFBFBF"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -927,13 +957,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+              <a:defRPr sz="900" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="595959"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1100220"/>
@@ -952,7 +983,7 @@
           <c:spPr>
             <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="d9d9d9"/>
+                <a:srgbClr val="D9D9D9"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -965,7 +996,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="bfbfbf"/>
+              <a:srgbClr val="BFBFBF"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -975,13 +1006,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+              <a:defRPr sz="900" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="595959"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="87998239"/>
@@ -990,7 +1022,7 @@
       </c:valAx>
       <c:spPr>
         <a:solidFill>
-          <a:srgbClr val="dae3f3"/>
+          <a:srgbClr val="DAE3F3"/>
         </a:solidFill>
         <a:ln w="0">
           <a:noFill/>
@@ -999,23 +1031,31 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:noFill/>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1024,7 +1064,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1400" spc="-1" strike="noStrike">
+              <a:defRPr sz="1400" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="595959"/>
                 </a:solidFill>
@@ -1032,7 +1072,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="0" sz="1400" spc="-1" strike="noStrike">
+              <a:rPr lang="ru-RU" sz="1400" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="595959"/>
                 </a:solidFill>
@@ -1043,6 +1083,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1058,25 +1099,22 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0363006581226186"/>
-          <c:y val="0.0254593175853018"/>
-          <c:w val="0.903429165223415"/>
-          <c:h val="0.777296587926509"/>
+          <c:x val="3.6300658122618602E-2"/>
+          <c:y val="2.5459317585301799E-2"/>
+          <c:w val="0.90342916522341499"/>
+          <c:h val="0.77729658792650902"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
-        <c:scatterStyle val="line"/>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4472c4"/>
-            </a:solidFill>
-            <a:ln cap="rnd" w="19080">
+            <a:ln w="19080" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="4472c4"/>
+                <a:srgbClr val="4472C4"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1085,18 +1123,26 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="r"/>
@@ -1105,8 +1151,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1156,37 +1203,50 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>-2.85714285714286</c:v>
+                  <c:v>-2.8571428571428572</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-2.14285714285714</c:v>
+                  <c:v>-2.1428571428571428</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-1.42857142857143</c:v>
+                  <c:v>-1.4285714285714286</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0.714285714285714</c:v>
+                  <c:v>-0.7142857142857143</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.714285714285714</c:v>
+                  <c:v>0.7142857142857143</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.42857142857143</c:v>
+                  <c:v>1.4285714285714286</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.14285714285714</c:v>
+                  <c:v>2.1428571428571428</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.85714285714286</c:v>
+                  <c:v>2.8571428571428572</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0A3B-4BB4-B912-69BA4E5C9897}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="53769816"/>
         <c:axId val="51738820"/>
       </c:scatterChart>
@@ -1201,7 +1261,7 @@
           <c:spPr>
             <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="d9d9d9"/>
+                <a:srgbClr val="D9D9D9"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1214,7 +1274,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="bfbfbf"/>
+              <a:srgbClr val="BFBFBF"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -1224,13 +1284,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+              <a:defRPr sz="900" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="595959"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="51738820"/>
@@ -1248,7 +1309,7 @@
           <c:spPr>
             <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="d9d9d9"/>
+                <a:srgbClr val="D9D9D9"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1261,7 +1322,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="bfbfbf"/>
+              <a:srgbClr val="BFBFBF"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -1271,13 +1332,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+              <a:defRPr sz="900" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="595959"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="53769816"/>
@@ -1293,23 +1355,29 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>13</xdr:col>
@@ -1323,14 +1391,14 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>149400</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Диаграмма 2"/>
+        <xdr:cNvPr id="2" name="Диаграмма 2"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="8768880" y="2828880"/>
-        <a:ext cx="6857640" cy="3152520"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1353,14 +1421,14 @@
       <xdr:row>27</xdr:row>
       <xdr:rowOff>148320</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Диаграмма 3"/>
+        <xdr:cNvPr id="3" name="Диаграмма 3"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="16419240" y="3029040"/>
-        <a:ext cx="5196240" cy="2742840"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1374,54 +1442,54 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
     <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1453,7 +1521,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1477,7 +1545,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1537,28 +1605,27 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O58"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.14"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="0" width="9.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.86"/>
+    <col min="1" max="1" width="10.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1591,959 +1658,959 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="9" t="n">
+      <c r="B2" s="8">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9">
+        <v>1</v>
+      </c>
+      <c r="D2" s="9">
         <v>-0.2</v>
       </c>
-      <c r="E2" s="9" t="n">
+      <c r="E2" s="9">
         <v>0.2</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="1">
         <v>-2</v>
       </c>
-      <c r="G2" s="9" t="n">
+      <c r="G2" s="9">
         <v>-0.7</v>
       </c>
-      <c r="H2" s="9" t="n">
+      <c r="H2" s="9">
         <v>-1.4</v>
       </c>
-      <c r="I2" s="8" t="n">
-        <f aca="false">$C2*$F2+$D2*$G2+$E2*$H2</f>
+      <c r="I2" s="8">
+        <f t="shared" ref="I2:I31" si="0">$C2*$F2+$D2*$G2+$E2*$H2</f>
         <v>-2.14</v>
       </c>
-      <c r="J2" s="9" t="n">
-        <f aca="false">IF(I2&gt;=0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K2" s="10" t="n">
-        <f aca="false">IF(OR(AND(J2=1,A2="+"),AND(J2=0,A2="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J2" s="9">
+        <f t="shared" ref="J2:J31" si="1">IF(I2&gt;=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="10">
+        <f t="shared" ref="K2:K31" si="2">IF(OR(AND(J2=1,A2="+"),AND(J2=0,A2="-")),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="9" t="n">
+      <c r="B3" s="8">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9">
+        <v>1</v>
+      </c>
+      <c r="D3" s="9">
         <v>-1.2</v>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="E3" s="9">
         <v>-0.5</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" s="1">
         <v>-2</v>
       </c>
-      <c r="G3" s="9" t="n">
+      <c r="G3" s="9">
         <v>-0.7</v>
       </c>
-      <c r="H3" s="9" t="n">
+      <c r="H3" s="9">
         <v>-1.4</v>
       </c>
-      <c r="I3" s="8" t="n">
-        <f aca="false">$C3*$F3+$D3*$G3+$E3*$H3</f>
-        <v>-0.46</v>
-      </c>
-      <c r="J3" s="9" t="n">
-        <f aca="false">IF(I3&gt;=0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="10" t="n">
-        <f aca="false">IF(OR(AND(J3=1,A3="+"),AND(J3=0,A3="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I3" s="8">
+        <f t="shared" si="0"/>
+        <v>-0.46000000000000019</v>
+      </c>
+      <c r="J3" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K3" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="9" t="n">
+      <c r="B4" s="8">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9">
+        <v>1</v>
+      </c>
+      <c r="D4" s="9">
         <v>-0.8</v>
       </c>
-      <c r="E4" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1" t="n">
+      <c r="E4" s="9">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
         <v>-2</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="9">
         <v>-0.7</v>
       </c>
-      <c r="H4" s="9" t="n">
+      <c r="H4" s="9">
         <v>-1.4</v>
       </c>
-      <c r="I4" s="8" t="n">
-        <f aca="false">$C4*$F4+$D4*$G4+$E4*$H4</f>
+      <c r="I4" s="8">
+        <f t="shared" si="0"/>
         <v>-2.84</v>
       </c>
-      <c r="J4" s="9" t="n">
-        <f aca="false">IF(I4&gt;=0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="10" t="n">
-        <f aca="false">IF(OR(AND(J4=1,A4="+"),AND(J4=0,A4="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J4" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K4" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="9" t="n">
+      <c r="B5" s="8">
+        <v>1</v>
+      </c>
+      <c r="C5" s="9">
+        <v>1</v>
+      </c>
+      <c r="D5" s="9">
         <v>-0.3</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="9">
         <v>1.2</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="1">
         <v>-2</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="9">
         <v>-0.7</v>
       </c>
-      <c r="H5" s="9" t="n">
+      <c r="H5" s="9">
         <v>-1.4</v>
       </c>
-      <c r="I5" s="8" t="n">
-        <f aca="false">$C5*$F5+$D5*$G5+$E5*$H5</f>
-        <v>-3.47</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <f aca="false">IF(I5&gt;=0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="10" t="n">
-        <f aca="false">IF(OR(AND(J5=1,A5="+"),AND(J5=0,A5="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I5" s="8">
+        <f t="shared" si="0"/>
+        <v>-3.4699999999999998</v>
+      </c>
+      <c r="J5" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="E6" s="9" t="n">
+      <c r="B6" s="8">
+        <v>1</v>
+      </c>
+      <c r="C6" s="9">
+        <v>1</v>
+      </c>
+      <c r="D6" s="9">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="E6" s="9">
         <v>0.5</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="1">
         <v>-2</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="9">
         <v>-0.7</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="H6" s="9">
         <v>-1.4</v>
       </c>
-      <c r="I6" s="8" t="n">
-        <f aca="false">$C6*$F6+$D6*$G6+$E6*$H6</f>
+      <c r="I6" s="8">
+        <f t="shared" si="0"/>
         <v>-1.93</v>
       </c>
-      <c r="J6" s="9" t="n">
-        <f aca="false">IF(I6&gt;=0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="10" t="n">
-        <f aca="false">IF(OR(AND(J6=1,A6="+"),AND(J6=0,A6="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J6" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="9" t="n">
+      <c r="B7" s="8">
+        <v>0</v>
+      </c>
+      <c r="C7" s="9">
+        <v>1</v>
+      </c>
+      <c r="D7" s="9">
         <v>0.7</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="9">
         <v>0.7</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="1">
         <v>-2</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="9">
         <v>-0.7</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="H7" s="9">
         <v>-1.4</v>
       </c>
-      <c r="I7" s="8" t="n">
-        <f aca="false">$C7*$F7+$D7*$G7+$E7*$H7</f>
-        <v>-3.47</v>
-      </c>
-      <c r="J7" s="9" t="n">
-        <f aca="false">IF(I7&gt;=0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="10" t="n">
-        <f aca="false">IF(OR(AND(J7=1,A7="+"),AND(J7=0,A7="-")),1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I7" s="8">
+        <f t="shared" si="0"/>
+        <v>-3.4699999999999998</v>
+      </c>
+      <c r="J7" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K7" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="9" t="n">
+      <c r="B8" s="8">
+        <v>0</v>
+      </c>
+      <c r="C8" s="9">
+        <v>1</v>
+      </c>
+      <c r="D8" s="9">
         <v>1.5</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="9">
         <v>1.4</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="F8" s="1">
         <v>-1</v>
       </c>
-      <c r="G8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="9" t="n">
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I8" s="8" t="n">
-        <f aca="false">$C8*$F8+$D8*$G8+$E8*$H8</f>
+      <c r="I8" s="8">
+        <f t="shared" si="0"/>
         <v>-1.98</v>
       </c>
-      <c r="J8" s="9" t="n">
-        <f aca="false">IF(I8&gt;=0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="10" t="n">
-        <f aca="false">IF(OR(AND(J8=1,A8="+"),AND(J8=0,A8="-")),1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J8" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="9" t="n">
+      <c r="B9" s="8">
+        <v>0</v>
+      </c>
+      <c r="C9" s="9">
+        <v>1</v>
+      </c>
+      <c r="D9" s="9">
         <v>0.8</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="9">
         <v>-0.5</v>
       </c>
-      <c r="F9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="9" t="n">
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="9">
         <v>1.5</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="9">
         <v>0.7</v>
       </c>
-      <c r="I9" s="8" t="n">
-        <f aca="false">$C9*$F9+$D9*$G9+$E9*$H9</f>
-        <v>0.85</v>
-      </c>
-      <c r="J9" s="9" t="n">
-        <f aca="false">IF(I9&gt;=0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="K9" s="10" t="n">
-        <f aca="false">IF(OR(AND(J9=1,A9="+"),AND(J9=0,A9="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I9" s="8">
+        <f t="shared" si="0"/>
+        <v>0.8500000000000002</v>
+      </c>
+      <c r="J9" s="9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K9" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="9" t="n">
+      <c r="B10" s="8">
+        <v>0</v>
+      </c>
+      <c r="C10" s="9">
+        <v>1</v>
+      </c>
+      <c r="D10" s="9">
         <v>-0.7</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="9">
         <v>-1.2</v>
       </c>
-      <c r="F10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="9" t="n">
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
         <v>1.5</v>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="H10" s="9">
         <v>0.7</v>
       </c>
-      <c r="I10" s="8" t="n">
-        <f aca="false">$C10*$F10+$D10*$G10+$E10*$H10</f>
-        <v>-1.89</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <f aca="false">IF(I10&gt;=0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="10" t="n">
-        <f aca="false">IF(OR(AND(J10=1,A10="+"),AND(J10=0,A10="-")),1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I10" s="8">
+        <f t="shared" si="0"/>
+        <v>-1.8899999999999997</v>
+      </c>
+      <c r="J10" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="13" t="n">
+      <c r="B11" s="12">
+        <v>0</v>
+      </c>
+      <c r="C11" s="13">
+        <v>1</v>
+      </c>
+      <c r="D11" s="13">
         <v>0.7</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="13">
         <v>-1.9</v>
       </c>
-      <c r="F11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="9" t="n">
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="9">
         <v>0.8</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H11" s="9">
         <v>-0.5</v>
       </c>
-      <c r="I11" s="12" t="n">
-        <f aca="false">$C11*$F11+$D11*$G11+$E11*$H11</f>
-        <v>2.51</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <f aca="false">IF(I11&gt;=0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="K11" s="14" t="n">
-        <f aca="false">IF(OR(AND(J11=1,A11="+"),AND(J11=0,A11="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I11" s="12">
+        <f t="shared" si="0"/>
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="J11" s="13">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K11" s="14">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="3"/>
-      <c r="C12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="9" t="n">
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="9">
         <v>-0.2</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="9">
         <v>0.2</v>
       </c>
-      <c r="F12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="9" t="n">
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="9">
         <v>0.8</v>
       </c>
-      <c r="H12" s="9" t="n">
+      <c r="H12" s="9">
         <v>-0.5</v>
       </c>
-      <c r="I12" s="3" t="n">
-        <f aca="false">$C12*$F12+$D12*$G12+$E12*$H12</f>
+      <c r="I12" s="3">
+        <f t="shared" si="0"/>
         <v>0.74</v>
       </c>
-      <c r="J12" s="4" t="n">
-        <f aca="false">IF(I12&gt;=0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <f aca="false">IF(OR(AND(J12=1,A12="+"),AND(J12=0,A12="-")),1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J12" s="4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K12" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="8"/>
-      <c r="C13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="9" t="n">
+      <c r="C13" s="9">
+        <v>1</v>
+      </c>
+      <c r="D13" s="9">
         <v>-1.2</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="9">
         <v>-0.5</v>
       </c>
-      <c r="F13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="9" t="n">
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="9">
+        <v>1</v>
+      </c>
+      <c r="H13" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I13" s="8" t="n">
-        <f aca="false">$C13*$F13+$D13*$G13+$E13*$H13</f>
+      <c r="I13" s="8">
+        <f t="shared" si="0"/>
         <v>-0.85</v>
       </c>
-      <c r="J13" s="9" t="n">
-        <f aca="false">IF(I13&gt;=0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <f aca="false">IF(OR(AND(J13=1,A13="+"),AND(J13=0,A13="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J13" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B14" s="8"/>
-      <c r="C14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="9" t="n">
+      <c r="C14" s="9">
+        <v>1</v>
+      </c>
+      <c r="D14" s="9">
         <v>-0.8</v>
       </c>
-      <c r="E14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="9" t="n">
+      <c r="E14" s="9">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>1</v>
+      </c>
+      <c r="H14" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I14" s="8" t="n">
-        <f aca="false">$C14*$F14+$D14*$G14+$E14*$H14</f>
+      <c r="I14" s="8">
+        <f t="shared" si="0"/>
         <v>-1.5</v>
       </c>
-      <c r="J14" s="9" t="n">
-        <f aca="false">IF(I14&gt;=0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="10" t="n">
-        <f aca="false">IF(OR(AND(J14=1,A14="+"),AND(J14=0,A14="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J14" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B15" s="8"/>
-      <c r="C15" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="9" t="n">
+      <c r="C15" s="9">
+        <v>1</v>
+      </c>
+      <c r="D15" s="9">
         <v>-0.3</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="9">
         <v>1.2</v>
       </c>
-      <c r="F15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="9" t="n">
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="9">
+        <v>1</v>
+      </c>
+      <c r="H15" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I15" s="8" t="n">
-        <f aca="false">$C15*$F15+$D15*$G15+$E15*$H15</f>
-        <v>-1.14</v>
-      </c>
-      <c r="J15" s="9" t="n">
-        <f aca="false">IF(I15&gt;=0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="10" t="n">
-        <f aca="false">IF(OR(AND(J15=1,A15="+"),AND(J15=0,A15="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I15" s="8">
+        <f t="shared" si="0"/>
+        <v>-1.1399999999999999</v>
+      </c>
+      <c r="J15" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="8"/>
-      <c r="C16" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="E16" s="9" t="n">
+      <c r="C16" s="9">
+        <v>1</v>
+      </c>
+      <c r="D16" s="9">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="E16" s="9">
         <v>0.5</v>
       </c>
-      <c r="F16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="9" t="n">
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>1</v>
+      </c>
+      <c r="H16" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I16" s="8" t="n">
-        <f aca="false">$C16*$F16+$D16*$G16+$E16*$H16</f>
-        <v>-1.45</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <f aca="false">IF(I16&gt;=0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="10" t="n">
-        <f aca="false">IF(OR(AND(J16=1,A16="+"),AND(J16=0,A16="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I16" s="8">
+        <f t="shared" si="0"/>
+        <v>-1.4500000000000002</v>
+      </c>
+      <c r="J16" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B17" s="8"/>
-      <c r="C17" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="9" t="n">
+      <c r="C17" s="9">
+        <v>1</v>
+      </c>
+      <c r="D17" s="9">
         <v>0.7</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="9">
         <v>0.7</v>
       </c>
-      <c r="F17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="9" t="n">
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>1</v>
+      </c>
+      <c r="H17" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I17" s="8" t="n">
-        <f aca="false">$C17*$F17+$D17*$G17+$E17*$H17</f>
-        <v>0.21</v>
-      </c>
-      <c r="J17" s="9" t="n">
-        <f aca="false">IF(I17&gt;=0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="K17" s="10" t="n">
-        <f aca="false">IF(OR(AND(J17=1,A17="+"),AND(J17=0,A17="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I17" s="8">
+        <f t="shared" si="0"/>
+        <v>0.21000000000000002</v>
+      </c>
+      <c r="J17" s="9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K17" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B18" s="8"/>
-      <c r="C18" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="9" t="n">
+      <c r="C18" s="9">
+        <v>1</v>
+      </c>
+      <c r="D18" s="9">
         <v>1.5</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="9">
         <v>1.4</v>
       </c>
-      <c r="F18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="9" t="n">
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>1</v>
+      </c>
+      <c r="H18" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I18" s="8" t="n">
-        <f aca="false">$C18*$F18+$D18*$G18+$E18*$H18</f>
-        <v>0.52</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <f aca="false">IF(I18&gt;=0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="K18" s="10" t="n">
-        <f aca="false">IF(OR(AND(J18=1,A18="+"),AND(J18=0,A18="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I18" s="8">
+        <f t="shared" si="0"/>
+        <v>0.52000000000000013</v>
+      </c>
+      <c r="J18" s="9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K18" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B19" s="8"/>
-      <c r="C19" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="9" t="n">
+      <c r="C19" s="9">
+        <v>1</v>
+      </c>
+      <c r="D19" s="9">
         <v>0.8</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="9">
         <v>-0.5</v>
       </c>
-      <c r="F19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="9" t="n">
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="9">
+        <v>1</v>
+      </c>
+      <c r="H19" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I19" s="8" t="n">
-        <f aca="false">$C19*$F19+$D19*$G19+$E19*$H19</f>
-        <v>1.15</v>
-      </c>
-      <c r="J19" s="9" t="n">
-        <f aca="false">IF(I19&gt;=0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="K19" s="10" t="n">
-        <f aca="false">IF(OR(AND(J19=1,A19="+"),AND(J19=0,A19="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I19" s="8">
+        <f t="shared" si="0"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J19" s="9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K19" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B20" s="8"/>
-      <c r="C20" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="9" t="n">
+      <c r="C20" s="9">
+        <v>1</v>
+      </c>
+      <c r="D20" s="9">
         <v>-0.7</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="9">
         <v>-1.2</v>
       </c>
-      <c r="F20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="9" t="n">
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="9">
+        <v>1</v>
+      </c>
+      <c r="H20" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I20" s="8" t="n">
-        <f aca="false">$C20*$F20+$D20*$G20+$E20*$H20</f>
-        <v>0.14</v>
-      </c>
-      <c r="J20" s="9" t="n">
-        <f aca="false">IF(I20&gt;=0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="K20" s="10" t="n">
-        <f aca="false">IF(OR(AND(J20=1,A20="+"),AND(J20=0,A20="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20" s="8">
+        <f t="shared" si="0"/>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J20" s="9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K20" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>11</v>
       </c>
       <c r="B21" s="12"/>
-      <c r="C21" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="13" t="n">
+      <c r="C21" s="13">
+        <v>1</v>
+      </c>
+      <c r="D21" s="13">
         <v>0.7</v>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="13">
         <v>-1.9</v>
       </c>
-      <c r="F21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="9" t="n">
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="9">
+        <v>1</v>
+      </c>
+      <c r="H21" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I21" s="12" t="n">
-        <f aca="false">$C21*$F21+$D21*$G21+$E21*$H21</f>
-        <v>2.03</v>
-      </c>
-      <c r="J21" s="13" t="n">
-        <f aca="false">IF(I21&gt;=0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="K21" s="14" t="n">
-        <f aca="false">IF(OR(AND(J21=1,A21="+"),AND(J21=0,A21="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I21" s="12">
+        <f t="shared" si="0"/>
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="J21" s="13">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K21" s="14">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>10</v>
       </c>
       <c r="B22" s="3"/>
-      <c r="C22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="9" t="n">
+      <c r="C22" s="4">
+        <v>1</v>
+      </c>
+      <c r="D22" s="9">
         <v>-0.2</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="9">
         <v>0.2</v>
       </c>
-      <c r="F22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="9" t="n">
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="9">
+        <v>1</v>
+      </c>
+      <c r="H22" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I22" s="3" t="n">
-        <f aca="false">$C22*$F22+$D22*$G22+$E22*$H22</f>
-        <v>-0.34</v>
-      </c>
-      <c r="J22" s="4" t="n">
-        <f aca="false">IF(I22&gt;=0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="6" t="n">
-        <f aca="false">IF(OR(AND(J22=1,A22="+"),AND(J22=0,A22="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I22" s="3">
+        <f t="shared" si="0"/>
+        <v>-0.33999999999999997</v>
+      </c>
+      <c r="J22" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="6">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B23" s="8"/>
-      <c r="C23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="9" t="n">
+      <c r="C23" s="9">
+        <v>1</v>
+      </c>
+      <c r="D23" s="9">
         <v>-1.2</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="9">
         <v>-0.5</v>
       </c>
-      <c r="F23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="9" t="n">
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="9">
+        <v>1</v>
+      </c>
+      <c r="H23" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I23" s="8" t="n">
-        <f aca="false">$C23*$F23+$D23*$G23+$E23*$H23</f>
+      <c r="I23" s="8">
+        <f t="shared" si="0"/>
         <v>-0.85</v>
       </c>
-      <c r="J23" s="9" t="n">
-        <f aca="false">IF(I23&gt;=0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K23" s="10" t="n">
-        <f aca="false">IF(OR(AND(J23=1,A23="+"),AND(J23=0,A23="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J23" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="8"/>
-      <c r="C24" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="9" t="n">
+      <c r="C24" s="9">
+        <v>1</v>
+      </c>
+      <c r="D24" s="9">
         <v>-0.8</v>
       </c>
-      <c r="E24" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="9" t="n">
+      <c r="E24" s="9">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>1</v>
+      </c>
+      <c r="H24" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I24" s="8" t="n">
-        <f aca="false">$C24*$F24+$D24*$G24+$E24*$H24</f>
+      <c r="I24" s="8">
+        <f t="shared" si="0"/>
         <v>-1.5</v>
       </c>
-      <c r="J24" s="9" t="n">
-        <f aca="false">IF(I24&gt;=0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="10" t="n">
-        <f aca="false">IF(OR(AND(J24=1,A24="+"),AND(J24=0,A24="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J24" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B25" s="8"/>
-      <c r="C25" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="9" t="n">
+      <c r="C25" s="9">
+        <v>1</v>
+      </c>
+      <c r="D25" s="9">
         <v>-0.3</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="9">
         <v>1.2</v>
       </c>
-      <c r="F25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="9" t="n">
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="9">
+        <v>1</v>
+      </c>
+      <c r="H25" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I25" s="8" t="n">
-        <f aca="false">$C25*$F25+$D25*$G25+$E25*$H25</f>
-        <v>-1.14</v>
-      </c>
-      <c r="J25" s="9" t="n">
-        <f aca="false">IF(I25&gt;=0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="10" t="n">
-        <f aca="false">IF(OR(AND(J25=1,A25="+"),AND(J25=0,A25="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="8">
+        <f t="shared" si="0"/>
+        <v>-1.1399999999999999</v>
+      </c>
+      <c r="J25" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B26" s="8"/>
-      <c r="C26" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="9" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="E26" s="9" t="n">
+      <c r="C26" s="9">
+        <v>1</v>
+      </c>
+      <c r="D26" s="9">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="E26" s="9">
         <v>0.5</v>
       </c>
-      <c r="F26" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="9" t="n">
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>1</v>
+      </c>
+      <c r="H26" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I26" s="8" t="n">
-        <f aca="false">$C26*$F26+$D26*$G26+$E26*$H26</f>
-        <v>-1.45</v>
-      </c>
-      <c r="J26" s="9" t="n">
-        <f aca="false">IF(I26&gt;=0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="10" t="n">
-        <f aca="false">IF(OR(AND(J26=1,A26="+"),AND(J26=0,A26="-")),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I26" s="8">
+        <f t="shared" si="0"/>
+        <v>-1.4500000000000002</v>
+      </c>
+      <c r="J26" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B27" s="8"/>
-      <c r="C27" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="9" t="n">
+      <c r="C27" s="9">
+        <v>1</v>
+      </c>
+      <c r="D27" s="9">
         <v>0.7</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="9">
         <v>0.7</v>
       </c>
-      <c r="F27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="9" t="n">
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="9">
+        <v>1</v>
+      </c>
+      <c r="H27" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I27" s="8" t="n">
-        <f aca="false">$C27*$F27+$D27*$G27+$E27*$H27</f>
-        <v>0.21</v>
-      </c>
-      <c r="J27" s="9" t="n">
-        <f aca="false">IF(I27&gt;=0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="K27" s="10" t="n">
-        <f aca="false">IF(OR(AND(J27=1,A27="+"),AND(J27=0,A27="-")),1,0)</f>
+      <c r="I27" s="8">
+        <f t="shared" si="0"/>
+        <v>0.21000000000000002</v>
+      </c>
+      <c r="J27" s="9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K27" s="10">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L27" s="16" t="s">
@@ -2556,241 +2623,236 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="8"/>
-      <c r="C28" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="9" t="n">
+      <c r="C28" s="9">
+        <v>1</v>
+      </c>
+      <c r="D28" s="9">
         <v>1.5</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="9">
         <v>1.4</v>
       </c>
-      <c r="F28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="9" t="n">
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="9">
+        <v>1</v>
+      </c>
+      <c r="H28" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I28" s="8" t="n">
-        <f aca="false">$C28*$F28+$D28*$G28+$E28*$H28</f>
-        <v>0.52</v>
-      </c>
-      <c r="J28" s="9" t="n">
-        <f aca="false">IF(I28&gt;=0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="K28" s="10" t="n">
-        <f aca="false">IF(OR(AND(J28=1,A28="+"),AND(J28=0,A28="-")),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="L28" s="0" t="n">
+      <c r="I28" s="8">
+        <f t="shared" si="0"/>
+        <v>0.52000000000000013</v>
+      </c>
+      <c r="J28" s="9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K28" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L28">
         <v>-2</v>
       </c>
-      <c r="M28" s="16" t="n">
-        <f aca="false">-(F$31+G$31*L28)/H$31</f>
-        <v>-2.85714285714286</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M28" s="16">
+        <f t="shared" ref="M28:M36" si="3">-(F$31+G$31*L28)/H$31</f>
+        <v>-2.8571428571428572</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B29" s="8"/>
-      <c r="C29" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="9" t="n">
+      <c r="C29" s="9">
+        <v>1</v>
+      </c>
+      <c r="D29" s="9">
         <v>0.8</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="9">
         <v>-0.5</v>
       </c>
-      <c r="F29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="9" t="n">
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="9">
+        <v>1</v>
+      </c>
+      <c r="H29" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I29" s="8" t="n">
-        <f aca="false">$C29*$F29+$D29*$G29+$E29*$H29</f>
-        <v>1.15</v>
-      </c>
-      <c r="J29" s="9" t="n">
-        <f aca="false">IF(I29&gt;=0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="K29" s="10" t="n">
-        <f aca="false">IF(OR(AND(J29=1,A29="+"),AND(J29=0,A29="-")),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="L29" s="0" t="n">
+      <c r="I29" s="8">
+        <f t="shared" si="0"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J29" s="9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K29" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L29">
         <v>-1.5</v>
       </c>
-      <c r="M29" s="16" t="n">
-        <f aca="false">-(F$31+G$31*L29)/H$31</f>
-        <v>-2.14285714285714</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M29" s="16">
+        <f t="shared" si="3"/>
+        <v>-2.1428571428571428</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B30" s="8"/>
-      <c r="C30" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="9" t="n">
+      <c r="C30" s="9">
+        <v>1</v>
+      </c>
+      <c r="D30" s="9">
         <v>-0.7</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="9">
         <v>-1.2</v>
       </c>
-      <c r="F30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="9" t="n">
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9">
+        <v>1</v>
+      </c>
+      <c r="H30" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I30" s="8" t="n">
-        <f aca="false">$C30*$F30+$D30*$G30+$E30*$H30</f>
-        <v>0.14</v>
-      </c>
-      <c r="J30" s="9" t="n">
-        <f aca="false">IF(I30&gt;=0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="K30" s="10" t="n">
-        <f aca="false">IF(OR(AND(J30=1,A30="+"),AND(J30=0,A30="-")),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="L30" s="0" t="n">
+      <c r="I30" s="8">
+        <f t="shared" si="0"/>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J30" s="9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K30" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L30">
         <v>-1</v>
       </c>
-      <c r="M30" s="16" t="n">
-        <f aca="false">-(F$31+G$31*L30)/H$31</f>
-        <v>-1.42857142857143</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M30" s="16">
+        <f t="shared" si="3"/>
+        <v>-1.4285714285714286</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>11</v>
       </c>
       <c r="B31" s="12"/>
-      <c r="C31" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="13" t="n">
+      <c r="C31" s="13">
+        <v>1</v>
+      </c>
+      <c r="D31" s="13">
         <v>0.7</v>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="13">
         <v>-1.9</v>
       </c>
-      <c r="F31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="9" t="n">
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="9">
+        <v>1</v>
+      </c>
+      <c r="H31" s="9">
         <v>-0.7</v>
       </c>
-      <c r="I31" s="12" t="n">
-        <f aca="false">$C31*$F31+$D31*$G31+$E31*$H31</f>
-        <v>2.03</v>
-      </c>
-      <c r="J31" s="13" t="n">
-        <f aca="false">IF(I31&gt;=0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="K31" s="14" t="n">
-        <f aca="false">IF(OR(AND(J31=1,A31="+"),AND(J31=0,A31="-")),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="L31" s="0" t="n">
+      <c r="I31" s="12">
+        <f t="shared" si="0"/>
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="J31" s="13">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K31" s="14">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L31">
         <v>-0.5</v>
       </c>
-      <c r="M31" s="16" t="n">
-        <f aca="false">-(F$31+G$31*L31)/H$31</f>
-        <v>-0.714285714285714</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="16" t="n">
-        <f aca="false">-(F$31+G$31*L32)/H$31</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L33" s="0" t="n">
+      <c r="M31" s="16">
+        <f t="shared" si="3"/>
+        <v>-0.7142857142857143</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" s="16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L33">
         <v>0.5</v>
       </c>
-      <c r="M33" s="16" t="n">
-        <f aca="false">-(F$31+G$31*L33)/H$31</f>
-        <v>0.714285714285714</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L34" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" s="16" t="n">
-        <f aca="false">-(F$31+G$31*L34)/H$31</f>
-        <v>1.42857142857143</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L35" s="0" t="n">
+      <c r="M33" s="16">
+        <f t="shared" si="3"/>
+        <v>0.7142857142857143</v>
+      </c>
+    </row>
+    <row r="34" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34" s="16">
+        <f t="shared" si="3"/>
+        <v>1.4285714285714286</v>
+      </c>
+    </row>
+    <row r="35" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L35">
         <v>1.5</v>
       </c>
-      <c r="M35" s="16" t="n">
-        <f aca="false">-(F$31+G$31*L35)/H$31</f>
-        <v>2.14285714285714</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L36" s="0" t="n">
+      <c r="M35" s="16">
+        <f t="shared" si="3"/>
+        <v>2.1428571428571428</v>
+      </c>
+    </row>
+    <row r="36" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L36">
         <v>2</v>
       </c>
-      <c r="M36" s="16" t="n">
-        <f aca="false">-(F$31+G$31*L36)/H$31</f>
-        <v>2.85714285714286</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M36" s="16">
+        <f t="shared" si="3"/>
+        <v>2.8571428571428572</v>
+      </c>
+    </row>
+    <row r="58" spans="6:8" x14ac:dyDescent="0.25">
       <c r="F58" s="1"/>
       <c r="G58" s="17"/>
       <c r="H58" s="17"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J32:J1048576 K1:K31">
-    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>